--- a/Result/profitability/4726.xlsx
+++ b/Result/profitability/4726.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM66"/>
+  <dimension ref="A1:AM67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.54625</v>
+        <v>-0.5075000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-21.19</v>
+        <v>-18.20375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -783,7 +783,7 @@
         <v>-0.655</v>
       </c>
       <c r="N3" t="n">
-        <v>-31.25625</v>
+        <v>-30.11375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.735</v>
+        <v>-0.7075</v>
       </c>
       <c r="N4" t="n">
-        <v>-62.4925</v>
+        <v>-55.56125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.84</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7625000000000001</v>
+        <v>-0.73</v>
       </c>
       <c r="N5" t="n">
-        <v>-49.7325</v>
+        <v>-48.22999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.73</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7712500000000001</v>
+        <v>-0.7425</v>
       </c>
       <c r="N6" t="n">
-        <v>-37.49875</v>
+        <v>-32.41999999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.04</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8225</v>
+        <v>-0.8412500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-30.70625</v>
+        <v>-32.05624999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -8810,6 +8810,133 @@
       </c>
       <c r="AM66" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>203</v>
+      </c>
+      <c r="D67" t="n">
+        <v>221</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-18</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-70</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-34.32%</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-85</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-83</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-0.5287500000000001</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-27.9525</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X67" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>-0.6987670776407864</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>-0.3939393939393939</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>-0.5707502374169041</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK67" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
